--- a/zwift_results.xlsx
+++ b/zwift_results.xlsx
@@ -1,39 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vvloeberghs\Documents\ZwiftPower_Scraper\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F6DBA2-ACE5-4651-B51B-BF6F812D08BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="31980" yWindow="3180" windowWidth="38700" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="ZwiftResults" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="75">
   <si>
     <t>rider_id</t>
   </si>
@@ -152,6 +133,9 @@
     <t>Rick Bonhof</t>
   </si>
   <si>
+    <t>Ralf Pompe (BEAT)</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
@@ -249,6 +233,9 @@
   </si>
   <si>
     <t>https://zwiftpower.com/profile.php?z=7794820</t>
+  </si>
+  <si>
+    <t>https://zwiftpower.com/profile.php?z=6815267</t>
   </si>
   <si>
     <t>DNS</t>
@@ -257,8 +244,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="hh:mm:ss"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,7 +313,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -335,21 +325,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -387,7 +369,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -421,7 +403,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -456,10 +437,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -632,24 +612,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="40.6640625" customWidth="1"/>
-    <col min="5" max="5" width="30.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="40.7109375" customWidth="1"/>
+    <col min="5" max="10" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -681,7 +655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>1407605</v>
       </c>
@@ -689,31 +663,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1">
-        <v>1.5891203703703699E-2</v>
+        <v>0.0158912037037037</v>
       </c>
       <c r="F2" s="1">
-        <v>1.773148148148148E-2</v>
+        <v>0.01773148148148148</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>6191115</v>
       </c>
@@ -721,31 +695,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1">
-        <v>1.592592592592593E-2</v>
+        <v>0.01592592592592593</v>
       </c>
       <c r="F3" s="1">
-        <v>1.771990740740741E-2</v>
+        <v>0.01771990740740741</v>
       </c>
       <c r="G3" s="1">
-        <v>2.2418981481481481E-2</v>
+        <v>0.02241898148148148</v>
       </c>
       <c r="H3" s="1">
-        <v>2.9722222222222219E-2</v>
+        <v>0.02972222222222222</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>315835</v>
       </c>
@@ -753,31 +727,31 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1">
-        <v>1.6261574074074071E-2</v>
+        <v>0.01626157407407407</v>
       </c>
       <c r="F4" s="1">
-        <v>1.7766203703703701E-2</v>
+        <v>0.0177662037037037</v>
       </c>
       <c r="G4" s="1">
-        <v>2.2719907407407411E-2</v>
+        <v>0.02271990740740741</v>
       </c>
       <c r="H4" s="1">
-        <v>3.1168981481481482E-2</v>
+        <v>0.03116898148148148</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>6198965</v>
       </c>
@@ -785,31 +759,31 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1">
-        <v>1.667824074074074E-2</v>
+        <v>0.01667824074074074</v>
       </c>
       <c r="F5" s="1">
-        <v>1.9490740740740739E-2</v>
+        <v>0.01949074074074074</v>
       </c>
       <c r="G5" s="1">
-        <v>2.3865740740740739E-2</v>
+        <v>0.02386574074074074</v>
       </c>
       <c r="H5" s="1">
-        <v>3.3148148148148149E-2</v>
+        <v>0.03314814814814815</v>
       </c>
       <c r="I5" s="1">
-        <v>4.3819444444444453E-2</v>
+        <v>0.04381944444444445</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>1995330</v>
       </c>
@@ -817,31 +791,31 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1">
-        <v>1.6793981481481479E-2</v>
+        <v>0.01679398148148148</v>
       </c>
       <c r="F6" s="1">
-        <v>1.891203703703704E-2</v>
+        <v>0.01891203703703704</v>
       </c>
       <c r="G6" s="1">
-        <v>2.4722222222222218E-2</v>
+        <v>0.02472222222222222</v>
       </c>
       <c r="H6" s="1">
-        <v>3.4907407407407408E-2</v>
+        <v>0.03490740740740741</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>1444220</v>
       </c>
@@ -849,31 +823,31 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1">
-        <v>1.681712962962963E-2</v>
+        <v>0.01681712962962963</v>
       </c>
       <c r="F7" s="1">
-        <v>1.9201388888888889E-2</v>
+        <v>0.01920138888888889</v>
       </c>
       <c r="G7" s="1">
-        <v>2.4120370370370368E-2</v>
+        <v>0.02412037037037037</v>
       </c>
       <c r="H7" s="1">
-        <v>3.1932870370370368E-2</v>
+        <v>0.03193287037037037</v>
       </c>
       <c r="I7" s="1">
-        <v>4.4097222222222232E-2</v>
+        <v>0.04409722222222223</v>
       </c>
       <c r="J7" s="1">
-        <v>1.072916666666667E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.01072916666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>403833</v>
       </c>
@@ -881,31 +855,31 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1">
-        <v>1.68287037037037E-2</v>
+        <v>0.0168287037037037</v>
       </c>
       <c r="F8" s="1">
-        <v>1.892361111111111E-2</v>
+        <v>0.01892361111111111</v>
       </c>
       <c r="G8" s="1">
-        <v>2.4259259259259262E-2</v>
+        <v>0.02425925925925926</v>
       </c>
       <c r="H8" s="1">
-        <v>3.2314814814814817E-2</v>
+        <v>0.03231481481481482</v>
       </c>
       <c r="I8" s="1">
-        <v>4.4444444444444453E-2</v>
+        <v>0.04444444444444445</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>4829079</v>
       </c>
@@ -913,31 +887,31 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1">
-        <v>1.68287037037037E-2</v>
+        <v>0.0168287037037037</v>
       </c>
       <c r="F9" s="1">
-        <v>1.8958333333333331E-2</v>
+        <v>0.01895833333333333</v>
       </c>
       <c r="G9" s="1">
-        <v>2.480324074074074E-2</v>
+        <v>0.02480324074074074</v>
       </c>
       <c r="H9" s="1">
-        <v>3.197916666666667E-2</v>
+        <v>0.03197916666666667</v>
       </c>
       <c r="I9" s="1">
-        <v>4.8564814814814818E-2</v>
+        <v>0.04856481481481482</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>4604753</v>
       </c>
@@ -945,31 +919,31 @@
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E10" s="1">
-        <v>1.684027777777778E-2</v>
+        <v>0.01684027777777778</v>
       </c>
       <c r="F10" s="1">
-        <v>1.9803240740740739E-2</v>
+        <v>0.01980324074074074</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H10" s="1">
-        <v>3.2372685185185178E-2</v>
+        <v>0.03237268518518518</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>4703851</v>
       </c>
@@ -977,31 +951,31 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1">
-        <v>1.699074074074074E-2</v>
+        <v>0.01699074074074074</v>
       </c>
       <c r="F11" s="1">
-        <v>1.9143518518518522E-2</v>
+        <v>0.01914351851851852</v>
       </c>
       <c r="G11" s="1">
-        <v>2.4699074074074071E-2</v>
+        <v>0.02469907407407407</v>
       </c>
       <c r="H11" s="1">
-        <v>3.229166666666667E-2</v>
+        <v>0.03229166666666667</v>
       </c>
       <c r="I11" s="1">
-        <v>4.583333333333333E-2</v>
+        <v>0.04583333333333333</v>
       </c>
       <c r="J11" s="1">
-        <v>1.096064814814815E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.01096064814814815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>1071478</v>
       </c>
@@ -1009,31 +983,31 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1">
-        <v>1.700231481481481E-2</v>
+        <v>0.01700231481481481</v>
       </c>
       <c r="F12" s="1">
-        <v>1.891203703703704E-2</v>
+        <v>0.01891203703703704</v>
       </c>
       <c r="G12" s="1">
-        <v>2.4409722222222222E-2</v>
+        <v>0.02440972222222222</v>
       </c>
       <c r="H12" s="1">
-        <v>3.2546296296296302E-2</v>
+        <v>0.0325462962962963</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>7581971</v>
       </c>
@@ -1041,31 +1015,31 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1">
-        <v>1.7152777777777781E-2</v>
+        <v>0.01715277777777778</v>
       </c>
       <c r="F13" s="1">
-        <v>1.954861111111111E-2</v>
+        <v>0.01954861111111111</v>
       </c>
       <c r="G13" s="1">
-        <v>2.5150462962962961E-2</v>
+        <v>0.02515046296296296</v>
       </c>
       <c r="H13" s="1">
-        <v>3.2893518518518523E-2</v>
+        <v>0.03289351851851852</v>
       </c>
       <c r="I13" s="1">
-        <v>4.4675925925925918E-2</v>
+        <v>0.04467592592592592</v>
       </c>
       <c r="J13" s="1">
-        <v>1.109953703703704E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.01109953703703704</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>1461772</v>
       </c>
@@ -1073,31 +1047,31 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1">
-        <v>1.726851851851852E-2</v>
+        <v>0.01726851851851852</v>
       </c>
       <c r="F14" s="1">
-        <v>1.893518518518519E-2</v>
+        <v>0.01893518518518519</v>
       </c>
       <c r="G14" s="1">
-        <v>2.5486111111111109E-2</v>
+        <v>0.02548611111111111</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="1">
-        <v>1.2048611111111111E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.01204861111111111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>167420</v>
       </c>
@@ -1105,31 +1079,31 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1">
-        <v>1.7337962962962961E-2</v>
+        <v>0.01733796296296296</v>
       </c>
       <c r="F15" s="1">
-        <v>1.9571759259259261E-2</v>
+        <v>0.01957175925925926</v>
       </c>
       <c r="G15" s="1">
-        <v>2.538194444444444E-2</v>
+        <v>0.02538194444444444</v>
       </c>
       <c r="H15" s="1">
-        <v>3.3194444444444443E-2</v>
+        <v>0.03319444444444444</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>462954</v>
       </c>
@@ -1137,31 +1111,31 @@
         <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16" s="1">
-        <v>1.7349537037037038E-2</v>
+        <v>0.01734953703703704</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>653693</v>
       </c>
@@ -1169,31 +1143,31 @@
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" s="1">
-        <v>1.7500000000000002E-2</v>
+        <v>0.0175</v>
       </c>
       <c r="F17" s="1">
-        <v>2.0034722222222221E-2</v>
+        <v>0.02003472222222222</v>
       </c>
       <c r="G17" s="1">
-        <v>2.6203703703703701E-2</v>
+        <v>0.0262037037037037</v>
       </c>
       <c r="H17" s="1">
-        <v>3.4143518518518517E-2</v>
+        <v>0.03414351851851852</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>3866542</v>
       </c>
@@ -1201,31 +1175,31 @@
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" s="1">
-        <v>1.7928240740740741E-2</v>
+        <v>0.01792824074074074</v>
       </c>
       <c r="F18" s="1">
-        <v>2.0381944444444449E-2</v>
+        <v>0.02038194444444445</v>
       </c>
       <c r="G18" s="1">
-        <v>2.6712962962962959E-2</v>
+        <v>0.02671296296296296</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J18" s="1">
-        <v>1.1875E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.011875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>1969</v>
       </c>
@@ -1233,31 +1207,31 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E19" s="1">
-        <v>1.7939814814814811E-2</v>
+        <v>0.01793981481481481</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G19" s="1">
-        <v>2.62962962962963E-2</v>
+        <v>0.0262962962962963</v>
       </c>
       <c r="H19" s="1">
-        <v>3.3981481481481481E-2</v>
+        <v>0.03398148148148148</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>851549</v>
       </c>
@@ -1265,31 +1239,31 @@
         <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E20" s="1">
-        <v>1.8078703703703701E-2</v>
+        <v>0.0180787037037037</v>
       </c>
       <c r="F20" s="1">
-        <v>2.0069444444444449E-2</v>
+        <v>0.02006944444444445</v>
       </c>
       <c r="G20" s="1">
-        <v>2.62962962962963E-2</v>
+        <v>0.0262962962962963</v>
       </c>
       <c r="H20" s="1">
-        <v>3.4131944444444437E-2</v>
+        <v>0.03413194444444444</v>
       </c>
       <c r="I20" s="1">
-        <v>4.6354166666666669E-2</v>
+        <v>0.04635416666666667</v>
       </c>
       <c r="J20" s="1">
-        <v>1.15625E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.0115625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>2678</v>
       </c>
@@ -1297,31 +1271,31 @@
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E21" s="1">
-        <v>1.8148148148148149E-2</v>
+        <v>0.01814814814814815</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>997312</v>
       </c>
@@ -1329,31 +1303,31 @@
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E22" s="1">
-        <v>1.8229166666666671E-2</v>
+        <v>0.01822916666666667</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>2821829</v>
       </c>
@@ -1361,31 +1335,31 @@
         <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E23" s="1">
-        <v>1.8356481481481481E-2</v>
+        <v>0.01835648148148148</v>
       </c>
       <c r="F23" s="1">
-        <v>2.104166666666667E-2</v>
+        <v>0.02104166666666667</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H23" s="1">
-        <v>3.6458333333333343E-2</v>
+        <v>0.03645833333333334</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>4851568</v>
       </c>
@@ -1393,31 +1367,31 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>499989</v>
       </c>
@@ -1425,31 +1399,31 @@
         <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="1">
-        <v>1.862268518518519E-2</v>
+        <v>0.01862268518518519</v>
       </c>
       <c r="F25" s="1">
-        <v>2.238425925925926E-2</v>
+        <v>0.02238425925925926</v>
       </c>
       <c r="G25" s="1">
-        <v>2.87037037037037E-2</v>
+        <v>0.0287037037037037</v>
       </c>
       <c r="H25" s="1">
-        <v>3.664351851851852E-2</v>
+        <v>0.03664351851851852</v>
       </c>
       <c r="I25" s="1">
-        <v>5.3229166666666668E-2</v>
+        <v>0.05322916666666667</v>
       </c>
       <c r="J25" s="1">
-        <v>1.2222222222222219E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.01222222222222222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>953960</v>
       </c>
@@ -1457,31 +1431,31 @@
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26" s="1">
-        <v>1.7743055555555561E-2</v>
+        <v>0.01774305555555556</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H26" s="1">
-        <v>3.2557870370370369E-2</v>
+        <v>0.03255787037037037</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>4807243</v>
       </c>
@@ -1489,31 +1463,31 @@
         <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E27" s="1">
-        <v>1.8796296296296301E-2</v>
+        <v>0.0187962962962963</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J27" s="1">
-        <v>1.217592592592593E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.01217592592592593</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>3345836</v>
       </c>
@@ -1521,31 +1495,31 @@
         <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E28" s="1">
-        <v>1.9340277777777779E-2</v>
+        <v>0.01934027777777778</v>
       </c>
       <c r="F28" s="1">
-        <v>2.209490740740741E-2</v>
+        <v>0.02209490740740741</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>1343449</v>
       </c>
@@ -1553,31 +1527,31 @@
         <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E29" s="1">
-        <v>2.1064814814814811E-2</v>
+        <v>0.02106481481481481</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>7794820</v>
       </c>
@@ -1585,65 +1559,95 @@
         <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E30" s="1">
-        <v>2.1226851851851851E-2</v>
+        <v>0.02122685185185185</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31">
+        <v>6815267</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0.01763888888888889</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0.01946759259259259</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0.02585648148148148</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0.03252314814814815</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="D6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="D8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="D10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="D11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="D12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="D13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="D14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="D15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="D16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="D18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="D19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="D21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="D22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="D23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="D24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="D25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="D26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="D27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="D28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="D29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="D30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D4" r:id="rId3"/>
+    <hyperlink ref="D5" r:id="rId4"/>
+    <hyperlink ref="D6" r:id="rId5"/>
+    <hyperlink ref="D7" r:id="rId6"/>
+    <hyperlink ref="D8" r:id="rId7"/>
+    <hyperlink ref="D9" r:id="rId8"/>
+    <hyperlink ref="D10" r:id="rId9"/>
+    <hyperlink ref="D11" r:id="rId10"/>
+    <hyperlink ref="D12" r:id="rId11"/>
+    <hyperlink ref="D13" r:id="rId12"/>
+    <hyperlink ref="D14" r:id="rId13"/>
+    <hyperlink ref="D15" r:id="rId14"/>
+    <hyperlink ref="D16" r:id="rId15"/>
+    <hyperlink ref="D17" r:id="rId16"/>
+    <hyperlink ref="D18" r:id="rId17"/>
+    <hyperlink ref="D19" r:id="rId18"/>
+    <hyperlink ref="D20" r:id="rId19"/>
+    <hyperlink ref="D21" r:id="rId20"/>
+    <hyperlink ref="D22" r:id="rId21"/>
+    <hyperlink ref="D23" r:id="rId22"/>
+    <hyperlink ref="D24" r:id="rId23"/>
+    <hyperlink ref="D25" r:id="rId24"/>
+    <hyperlink ref="D26" r:id="rId25"/>
+    <hyperlink ref="D27" r:id="rId26"/>
+    <hyperlink ref="D28" r:id="rId27"/>
+    <hyperlink ref="D29" r:id="rId28"/>
+    <hyperlink ref="D30" r:id="rId29"/>
+    <hyperlink ref="D31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Confidential - External</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>